--- a/esyluban/examples/release/DataTables/test/multi_column.xlsx
+++ b/esyluban/examples/release/DataTables/test/multi_column.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1">
@@ -583,7 +583,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
@@ -653,55 +653,10 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
